--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/06,26/22,06,26 Останкино КИ/КИ + ЗПФ/Донецк/Дв.Останкино Колбаса от 22,06,26, Донецк (согласовал Лыгин).xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/06,26/22,06,26 Останкино КИ/КИ + ЗПФ/Донецк/Дв.Останкино Колбаса от 22,06,26, Донецк (согласовал Лыгин).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\06,26\24,06,26 Останкино КИ\КИ + ЗПФ\Донецк\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\06,26\22,06,26 Останкино КИ\КИ + ЗПФ\Донецк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D563FAC-677E-498E-BCB1-CD6EF0F57D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC2BEC7-064D-42E1-8C24-DF807A165332}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,15 @@
     <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
   </externalReferences>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -730,7 +738,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="TDSheet"/>
@@ -7783,7 +7791,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="TDSheet"/>
@@ -9375,7 +9383,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="TDSheet"/>
@@ -13902,9 +13910,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -13942,9 +13950,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -13977,9 +13985,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -14012,9 +14037,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -14203,7 +14245,9 @@
     <col min="8" max="18" width="7.33203125" customWidth="1"/>
     <col min="19" max="19" width="7.33203125" style="42" customWidth="1"/>
     <col min="20" max="21" width="7.33203125" style="38" customWidth="1"/>
-    <col min="22" max="32" width="7.33203125" customWidth="1"/>
+    <col min="22" max="22" width="7.33203125" customWidth="1"/>
+    <col min="23" max="23" width="5" customWidth="1"/>
+    <col min="24" max="32" width="7.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:83" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
